--- a/v4/03_extracted/SituationChap_VALIDATION_2023.xlsx
+++ b/v4/03_extracted/SituationChap_VALIDATION_2023.xlsx
@@ -1497,34 +1497,34 @@
         <v>420373.8</v>
       </c>
       <c r="M13" t="n">
-        <v>-2850000</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>778</v>
+        <v>100</v>
       </c>
       <c r="O13" t="n">
-        <v>-2850000</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>778</v>
+        <v>100</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2850000</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>778</v>
+        <v>100</v>
       </c>
       <c r="S13" t="n">
-        <v>-2850000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>778</v>
+        <v>100</v>
       </c>
       <c r="U13" t="n">
-        <v>-2850000</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>778</v>
+        <v>100</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="X13" t="n">
-        <v>778</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1753,42 +1753,42 @@
         <v>196564.1</v>
       </c>
       <c r="M16" t="n">
-        <v>-1800000</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1015.7</v>
+        <v>100</v>
       </c>
       <c r="O16" t="n">
-        <v>-1192264.34</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>706.6</v>
+        <v>100</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1461312.13</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>843.4</v>
+        <v>100</v>
       </c>
       <c r="S16" t="n">
-        <v>-1800000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1015.7</v>
+        <v>100</v>
       </c>
       <c r="U16" t="n">
-        <v>-1192767.21</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>706.8</v>
+        <v>100</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>linear_trend</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>706.6</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -2005,42 +2005,42 @@
         <v>1130400.26</v>
       </c>
       <c r="M19" t="n">
-        <v>-838878.6800000001</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>174.2</v>
+        <v>100</v>
       </c>
       <c r="O19" t="n">
-        <v>-513701.33</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>145.4</v>
+        <v>100</v>
       </c>
       <c r="Q19" t="n">
-        <v>-549832.15</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>148.6</v>
+        <v>100</v>
       </c>
       <c r="S19" t="n">
-        <v>-622093.78</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>155</v>
+        <v>100</v>
       </c>
       <c r="U19" t="n">
-        <v>-513678.76</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>145.4</v>
+        <v>100</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>exp_smoothing</t>
+          <t>linear_trend</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>145.4</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20">
@@ -2621,42 +2621,42 @@
         <v>196225.2</v>
       </c>
       <c r="M26" t="n">
-        <v>-6135234.02</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3226.6</v>
+        <v>100</v>
       </c>
       <c r="O26" t="n">
-        <v>-1908180.59</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1072.4</v>
+        <v>100</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2377853.19</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1311.8</v>
+        <v>100</v>
       </c>
       <c r="S26" t="n">
-        <v>-3317198.4</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>1790.5</v>
+        <v>100</v>
       </c>
       <c r="U26" t="n">
-        <v>-1911720.69</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1074.2</v>
+        <v>100</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>linear_trend</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>1072.4</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27">
@@ -5833,34 +5833,34 @@
         <v>619629.13</v>
       </c>
       <c r="M63" t="n">
-        <v>-6000000</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>1068.3</v>
+        <v>100</v>
       </c>
       <c r="O63" t="n">
-        <v>-6000000</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>1068.3</v>
+        <v>100</v>
       </c>
       <c r="Q63" t="n">
-        <v>-6000000</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>1068.3</v>
+        <v>100</v>
       </c>
       <c r="S63" t="n">
-        <v>-6000000</v>
+        <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>1068.3</v>
+        <v>100</v>
       </c>
       <c r="U63" t="n">
-        <v>-6000000</v>
+        <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>1068.3</v>
+        <v>100</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         </is>
       </c>
       <c r="X63" t="n">
-        <v>1068.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64">
@@ -8353,42 +8353,42 @@
         <v>233385.4</v>
       </c>
       <c r="M92" t="n">
-        <v>-2326316</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>1096.8</v>
+        <v>100</v>
       </c>
       <c r="O92" t="n">
-        <v>-1200585.16</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>614.4</v>
+        <v>100</v>
       </c>
       <c r="Q92" t="n">
-        <v>-1424379.13</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>710.3</v>
+        <v>100</v>
       </c>
       <c r="S92" t="n">
-        <v>-1871967.08</v>
+        <v>0</v>
       </c>
       <c r="T92" t="n">
-        <v>902.1</v>
+        <v>100</v>
       </c>
       <c r="U92" t="n">
-        <v>-1201003.45</v>
+        <v>0</v>
       </c>
       <c r="V92" t="n">
-        <v>614.6</v>
+        <v>100</v>
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>linear_trend</t>
         </is>
       </c>
       <c r="X92" t="n">
-        <v>614.4</v>
+        <v>100</v>
       </c>
     </row>
     <row r="93">
@@ -8441,34 +8441,34 @@
         <v>3111379.4</v>
       </c>
       <c r="M93" t="n">
-        <v>-4712410</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>251.5</v>
+        <v>100</v>
       </c>
       <c r="O93" t="n">
-        <v>-4712410</v>
+        <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>251.5</v>
+        <v>100</v>
       </c>
       <c r="Q93" t="n">
-        <v>-4712410</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>251.5</v>
+        <v>100</v>
       </c>
       <c r="S93" t="n">
-        <v>-4712410</v>
+        <v>0</v>
       </c>
       <c r="T93" t="n">
-        <v>251.5</v>
+        <v>100</v>
       </c>
       <c r="U93" t="n">
-        <v>-4712410</v>
+        <v>0</v>
       </c>
       <c r="V93" t="n">
-        <v>251.5</v>
+        <v>100</v>
       </c>
       <c r="W93" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         </is>
       </c>
       <c r="X93" t="n">
-        <v>251.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="94">
@@ -9161,22 +9161,22 @@
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="n">
-        <v>-3533367</v>
+        <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>5841.8</v>
+        <v>100</v>
       </c>
       <c r="Q102" t="n">
-        <v>-3533367</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>5841.8</v>
+        <v>100</v>
       </c>
       <c r="S102" t="n">
-        <v>-3533367</v>
+        <v>0</v>
       </c>
       <c r="T102" t="n">
-        <v>5841.8</v>
+        <v>100</v>
       </c>
       <c r="U102" t="inlineStr"/>
       <c r="V102" t="inlineStr"/>
@@ -9186,7 +9186,7 @@
         </is>
       </c>
       <c r="X102" t="n">
-        <v>5841.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="103">
@@ -9241,22 +9241,22 @@
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="n">
-        <v>-188784</v>
+        <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>101.9</v>
+        <v>100</v>
       </c>
       <c r="Q103" t="n">
-        <v>-188784</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>101.9</v>
+        <v>100</v>
       </c>
       <c r="S103" t="n">
-        <v>-188784</v>
+        <v>0</v>
       </c>
       <c r="T103" t="n">
-        <v>101.9</v>
+        <v>100</v>
       </c>
       <c r="U103" t="inlineStr"/>
       <c r="V103" t="inlineStr"/>
@@ -9266,7 +9266,7 @@
         </is>
       </c>
       <c r="X103" t="n">
-        <v>101.9</v>
+        <v>100</v>
       </c>
     </row>
     <row r="104">
@@ -9409,22 +9409,22 @@
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="n">
-        <v>-332534</v>
+        <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>173.6</v>
+        <v>100</v>
       </c>
       <c r="Q105" t="n">
-        <v>-332534</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>173.6</v>
+        <v>100</v>
       </c>
       <c r="S105" t="n">
-        <v>-332534</v>
+        <v>0</v>
       </c>
       <c r="T105" t="n">
-        <v>173.6</v>
+        <v>100</v>
       </c>
       <c r="U105" t="inlineStr"/>
       <c r="V105" t="inlineStr"/>
@@ -9434,7 +9434,7 @@
         </is>
       </c>
       <c r="X105" t="n">
-        <v>173.6</v>
+        <v>100</v>
       </c>
     </row>
     <row r="106">
@@ -10561,19 +10561,19 @@
         <v>420373.8</v>
       </c>
       <c r="M13" t="n">
-        <v>-2850000</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>5754580.86</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-3270373.8</v>
+        <v>-420373.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>778</v>
+        <v>100</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -10782,23 +10782,23 @@
         <v>196564.1</v>
       </c>
       <c r="M16" t="n">
-        <v>-1192264.34</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1090681.86</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-1388828.44</v>
+        <v>-196564.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>706.6</v>
+        <v>100</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>linear_trend</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -10997,23 +10997,23 @@
         <v>1130400.26</v>
       </c>
       <c r="M19" t="n">
-        <v>-513678.76</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-207098.62</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-1644079.02</v>
+        <v>-1130400.26</v>
       </c>
       <c r="Q19" t="n">
-        <v>145.4</v>
+        <v>100</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>exp_smoothing</t>
+          <t>linear_trend</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -11522,23 +11522,23 @@
         <v>196225.2</v>
       </c>
       <c r="M26" t="n">
-        <v>-1908180.59</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>2077123.6</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>-2104405.79</v>
+        <v>-196225.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>1072.4</v>
+        <v>100</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>linear_trend</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -14277,19 +14277,19 @@
         <v>619629.13</v>
       </c>
       <c r="M63" t="n">
-        <v>-6000000</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>16796892.85</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>-6619629.13</v>
+        <v>-619629.13</v>
       </c>
       <c r="Q63" t="n">
-        <v>1068.3</v>
+        <v>100</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
@@ -16428,23 +16428,23 @@
         <v>233385.4</v>
       </c>
       <c r="M92" t="n">
-        <v>-1200585.16</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
         <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>698369.66</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>-1433970.56</v>
+        <v>-233385.4</v>
       </c>
       <c r="Q92" t="n">
-        <v>614.4</v>
+        <v>100</v>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>linear_trend</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -16503,19 +16503,19 @@
         <v>3111379.4</v>
       </c>
       <c r="M93" t="n">
-        <v>-4712410</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
         <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>6097972.21</v>
+        <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>-7823789.4</v>
+        <v>-3111379.4</v>
       </c>
       <c r="Q93" t="n">
-        <v>251.5</v>
+        <v>100</v>
       </c>
       <c r="R93" t="inlineStr">
         <is>
@@ -17144,15 +17144,15 @@
         <v>61538</v>
       </c>
       <c r="M102" t="n">
-        <v>-3533367</v>
+        <v>0</v>
       </c>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="n">
-        <v>-3594905</v>
+        <v>-61538</v>
       </c>
       <c r="Q102" t="n">
-        <v>5841.8</v>
+        <v>100</v>
       </c>
       <c r="R102" t="inlineStr">
         <is>
@@ -17215,15 +17215,15 @@
         <v>10089787</v>
       </c>
       <c r="M103" t="n">
-        <v>-188784</v>
+        <v>0</v>
       </c>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="n">
-        <v>-10278571</v>
+        <v>-10089787</v>
       </c>
       <c r="Q103" t="n">
-        <v>101.9</v>
+        <v>100</v>
       </c>
       <c r="R103" t="inlineStr">
         <is>
@@ -17361,15 +17361,15 @@
         <v>451660</v>
       </c>
       <c r="M105" t="n">
-        <v>-332534</v>
+        <v>0</v>
       </c>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="n">
-        <v>-784194</v>
+        <v>-451660</v>
       </c>
       <c r="Q105" t="n">
-        <v>173.6</v>
+        <v>100</v>
       </c>
       <c r="R105" t="inlineStr">
         <is>
